--- a/grc_wisdom_api/scripts/verify/_tmp_reports/Issue_register.xlsx
+++ b/grc_wisdom_api/scripts/verify/_tmp_reports/Issue_register.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="56">
   <si>
     <t>Issue Register</t>
   </si>
@@ -32,7 +32,7 @@
     <t>Generated at</t>
   </si>
   <si>
-    <t>2026-08-16 17:58 UTC</t>
+    <t>2026-08-17 15:43 UTC</t>
   </si>
   <si>
     <t>Visibility</t>
@@ -107,19 +107,19 @@
     <t>CAPAssigned</t>
   </si>
   <si>
-    <t>Alaa Tamimi</t>
-  </si>
-  <si>
-    <t>Rami Khalil</t>
-  </si>
-  <si>
-    <t>2026-06-26</t>
-  </si>
-  <si>
-    <t>2026-08-25</t>
-  </si>
-  <si>
-    <t>50</t>
+    <t>Hassan Rahman</t>
+  </si>
+  <si>
+    <t>Mahmoud Abdulaziz</t>
+  </si>
+  <si>
+    <t>2026-07-01</t>
+  </si>
+  <si>
+    <t>2026-08-30</t>
+  </si>
+  <si>
+    <t>47</t>
   </si>
   <si>
     <t>AUD-2026-02-F1</t>
@@ -134,97 +134,52 @@
     <t>High</t>
   </si>
   <si>
-    <t>Mahmoud Abdulaziz</t>
-  </si>
-  <si>
-    <t>2026-07-08</t>
-  </si>
-  <si>
-    <t>2026-08-07</t>
-  </si>
-  <si>
-    <t>38</t>
+    <t>Salma Noor</t>
+  </si>
+  <si>
+    <t>2026-07-13</t>
+  </si>
+  <si>
+    <t>2026-08-12</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>AUD-2026-01-F1</t>
+  </si>
+  <si>
+    <t>Q2 recertification was not completed for two systems.</t>
+  </si>
+  <si>
+    <t>Closed</t>
+  </si>
+  <si>
+    <t>ISS-2026-001</t>
+  </si>
+  <si>
+    <t>SelfIdentified</t>
+  </si>
+  <si>
+    <t>RCSA-2026-01</t>
+  </si>
+  <si>
+    <t>Self-assessed ineffective control: AC-02</t>
+  </si>
+  <si>
+    <t>Open</t>
+  </si>
+  <si>
+    <t>2026-08-09</t>
+  </si>
+  <si>
+    <t>2026-10-08</t>
   </si>
   <si>
     <t>8</t>
-  </si>
-  <si>
-    <t>AUD-2032-06-F1</t>
-  </si>
-  <si>
-    <t>AUD-2032-06</t>
-  </si>
-  <si>
-    <t>3 of 25 payments were released with a single approval.</t>
-  </si>
-  <si>
-    <t>Mehdi Tantaoui</t>
-  </si>
-  <si>
-    <t>Shahd Hamdan</t>
-  </si>
-  <si>
-    <t>2026-08-16</t>
-  </si>
-  <si>
-    <t>2026-09-15</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>AUD-2026-01-F1</t>
-  </si>
-  <si>
-    <t>Q2 recertification was not completed for two systems.</t>
-  </si>
-  <si>
-    <t>Closed</t>
-  </si>
-  <si>
-    <t>AUD-2033-08-F1</t>
-  </si>
-  <si>
-    <t>AUD-2033-08</t>
-  </si>
-  <si>
-    <t>ISS-2026-001</t>
-  </si>
-  <si>
-    <t>SelfIdentified</t>
-  </si>
-  <si>
-    <t>RCSA-2026-01</t>
-  </si>
-  <si>
-    <t>Self-assessed ineffective control: CRY-01</t>
-  </si>
-  <si>
-    <t>Open</t>
-  </si>
-  <si>
-    <t>Ibrahim Abdulaziz</t>
-  </si>
-  <si>
-    <t>2026-08-04</t>
-  </si>
-  <si>
-    <t>2026-10-03</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>AUD-2031-04-F1</t>
-  </si>
-  <si>
-    <t>AUD-2031-04</t>
-  </si>
-  <si>
-    <t>PendingClosure</t>
-  </si>
-  <si>
-    <t>Abdullah Alfifi</t>
   </si>
 </sst>
 </file>
@@ -710,7 +665,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O8"/>
+  <dimension ref="A1:O5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -881,31 +836,31 @@
         <v>26</v>
       </c>
       <c r="E4" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="7" t="s">
         <v>46</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>47</v>
       </c>
       <c r="G4" s="7" t="s">
         <v>39</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="N4" s="7" t="s">
         <v>26</v>
@@ -916,189 +871,48 @@
     </row>
     <row r="5" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="I5" s="7" t="s">
         <v>31</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="M5" s="7" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="N5" s="7" t="s">
         <v>26</v>
       </c>
       <c r="O5" s="7" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="I6" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="J6" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="K6" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="L6" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="M6" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="N6" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="O6" s="7" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="I7" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="J7" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="K7" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="L7" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="M7" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="N7" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="O7" s="7" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="I8" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="K8" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="L8" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="M8" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="N8" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="O8" s="7" t="s">
         <v>26</v>
       </c>
     </row>
